--- a/49911_Intercuenca_49911/_raw_reportes_xlsx/IDConfig_65195_completo.xlsx
+++ b/49911_Intercuenca_49911/_raw_reportes_xlsx/IDConfig_65195_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R0f0ab139b722474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbe037417108a40be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,546 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>15/08/2026</x:t>
         </x:is>
       </x:c>

--- a/49911_Intercuenca_49911/_raw_reportes_xlsx/IDConfig_65195_completo.xlsx
+++ b/49911_Intercuenca_49911/_raw_reportes_xlsx/IDConfig_65195_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rbe037417108a40be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rb5fb72de4edf49ac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,2766 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>10/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.1820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.1420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.1020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.0520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.0120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.5920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.6920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.7520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.8720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    121.9920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.0220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.0620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.1020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    123.0220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.9420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8920</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8420</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.8120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.7020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.6320</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.5120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.4620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2720</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.2820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3020</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3120</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>06:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3220</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>18:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3520</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>14:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3620</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>10:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>    122.3820</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>24/08/2026</x:t>
         </x:is>
       </x:c>
